--- a/plot_Tutorial 2 barras - Copia.xlsx
+++ b/plot_Tutorial 2 barras - Copia.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Projeto_Regiao_Flexibilidade\PyTSOFlex\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541504EC-0782-416E-B8FB-017A81C27736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$51</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="115">
   <si>
     <t>Ângulo</t>
   </si>
@@ -344,13 +353,28 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Violação de Tensão sem contingência</t>
+  </si>
+  <si>
+    <t>Violação de Fluxo sem contingência</t>
+  </si>
+  <si>
+    <t>Divergência sem contingência</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Caso Base</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,13 +411,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -431,7 +463,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -465,6 +497,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -499,9 +532,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -674,11 +708,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -703,8 +747,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -729,8 +776,11 @@
       <c r="H2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -746,8 +796,11 @@
       <c r="E3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -763,8 +816,11 @@
       <c r="E4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -780,8 +836,11 @@
       <c r="E5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -797,8 +856,11 @@
       <c r="E6" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -814,8 +876,11 @@
       <c r="E7" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -831,8 +896,11 @@
       <c r="E8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -848,8 +916,11 @@
       <c r="E9" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -865,8 +936,11 @@
       <c r="E10" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -882,8 +956,11 @@
       <c r="F11" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -899,8 +976,11 @@
       <c r="E12" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -916,8 +996,11 @@
       <c r="F13" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -933,8 +1016,11 @@
       <c r="F14" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -950,8 +1036,11 @@
       <c r="H15" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -967,8 +1056,11 @@
       <c r="H16" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -984,8 +1076,11 @@
       <c r="H17" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1001,8 +1096,11 @@
       <c r="E18" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1018,8 +1116,11 @@
       <c r="E19" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1035,8 +1136,11 @@
       <c r="E20" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1052,8 +1156,11 @@
       <c r="E21" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1069,8 +1176,11 @@
       <c r="H22" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1086,8 +1196,11 @@
       <c r="E23" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1216,11 @@
       <c r="F24" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1120,8 +1236,11 @@
       <c r="F25" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1137,8 +1256,11 @@
       <c r="E26" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1154,8 +1276,11 @@
       <c r="F27" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1171,8 +1296,11 @@
       <c r="E28" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="I28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -1188,8 +1316,11 @@
       <c r="F29" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="I29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1205,8 +1336,11 @@
       <c r="H30" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="I30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>20</v>
       </c>
@@ -1222,8 +1356,11 @@
       <c r="F31" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="I31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -1239,8 +1376,11 @@
       <c r="H32" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="I32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -1256,8 +1396,11 @@
       <c r="F33" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="I33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1273,8 +1416,11 @@
       <c r="F34" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="I34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -1290,8 +1436,11 @@
       <c r="H35" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="I35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -1307,8 +1456,11 @@
       <c r="F36" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="I36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -1324,8 +1476,11 @@
       <c r="H37" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="I37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>22</v>
       </c>
@@ -1341,8 +1496,11 @@
       <c r="F38" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="I38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -1358,8 +1516,11 @@
       <c r="H39" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="I39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1375,8 +1536,11 @@
       <c r="F40" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="I40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -1392,8 +1556,11 @@
       <c r="H41" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="I41" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -1409,8 +1576,11 @@
       <c r="H42" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="I42" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -1426,8 +1596,11 @@
       <c r="H43" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="I43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>24</v>
       </c>
@@ -1443,8 +1616,11 @@
       <c r="F44" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="I44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -1460,8 +1636,11 @@
       <c r="H45" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="I45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1477,8 +1656,11 @@
       <c r="H46" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="I46" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1494,8 +1676,11 @@
       <c r="H47" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="I47" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -1511,8 +1696,11 @@
       <c r="H48" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="I48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -1528,8 +1716,11 @@
       <c r="H49" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="I49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>19</v>
       </c>
@@ -1545,8 +1736,11 @@
       <c r="H50" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="I50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -1562,8 +1756,12 @@
       <c r="H51" t="s">
         <v>108</v>
       </c>
+      <c r="I51" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>